--- a/api/templates/xpert_test_activities_report/vi.xlsx
+++ b/api/templates/xpert_test_activities_report/vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\xpert_test_activities_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C677E1B-15F1-4649-AAA4-3D202B632A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FE828A-051D-49D7-A916-C6A8C2A46338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0364F5F4-369F-49C4-9927-8F02FAEEE91E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0364F5F4-369F-49C4-9927-8F02FAEEE91E}"/>
   </bookViews>
   <sheets>
     <sheet name="M4B2.BCHĐ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <r>
       <t xml:space="preserve">                            BỘ Y TẾ                                                                                                             </t>
@@ -62,9 +62,6 @@
     <t xml:space="preserve">Người báo cáo: </t>
   </si>
   <si>
-    <t xml:space="preserve">Số điện thoại:                    Email:   </t>
-  </si>
-  <si>
     <t>Nội dung</t>
   </si>
   <si>
@@ -164,10 +161,28 @@
     <t>(ký, ghi rõ họ tên)</t>
   </si>
   <si>
-    <t>Phạm vi ngày</t>
-  </si>
-  <si>
     <t>Các mã lỗi khác</t>
+  </si>
+  <si>
+    <t>&lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;UserFullName&gt;</t>
+  </si>
+  <si>
+    <t>Số điện thoại:</t>
+  </si>
+  <si>
+    <t>&lt;UserMobilePhone&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: </t>
+  </si>
+  <si>
+    <t>&lt;UserEmail&gt;</t>
   </si>
 </sst>
 </file>
@@ -338,7 +353,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -414,18 +429,29 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -433,46 +459,49 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -791,14 +820,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0357BB-256E-4D58-AF42-D62435F49B44}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="46.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:9" ht="15.75">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -808,7 +837,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75">
+    <row r="2" spans="1:9" ht="15.75">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -818,7 +847,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -826,264 +855,277 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" ht="20.25">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:9" ht="20.25">
+      <c r="A4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25">
-      <c r="A5" s="23" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.5">
-      <c r="A6" s="24" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.5">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.5">
+      <c r="B6" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.5">
+      <c r="B7" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5">
       <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="28" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="16.5">
+      <c r="A10" s="32" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5">
-      <c r="A10" s="30" t="s">
+      <c r="B10" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16.5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="27" t="s">
+    <row r="11" spans="1:9" ht="16.5">
+      <c r="A11" s="33"/>
+      <c r="B11" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="16.5">
+      <c r="A12" s="33"/>
+      <c r="B12" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5">
-      <c r="A12" s="31"/>
-      <c r="B12" s="27" t="s">
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5">
+      <c r="A13" s="33"/>
+      <c r="B13" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
-      <c r="A13" s="31"/>
-      <c r="B13" s="27" t="s">
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5">
+      <c r="A14" s="33"/>
+      <c r="B14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5">
-      <c r="A14" s="31"/>
-      <c r="B14" s="29" t="s">
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5">
+      <c r="A15" s="33"/>
+      <c r="B15" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="31"/>
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5">
+      <c r="A16" s="34"/>
+      <c r="B16" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5">
-      <c r="A16" s="32"/>
-      <c r="B16" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.5">
+      <c r="A18" s="33"/>
+      <c r="B18" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="31"/>
-      <c r="B18" s="27" t="s">
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.5">
+      <c r="A19" s="33"/>
+      <c r="B19" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="31"/>
-      <c r="B19" s="27" t="s">
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.5">
+      <c r="A20" s="33"/>
+      <c r="B20" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="31"/>
-      <c r="B20" s="27" t="s">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="16.5">
+      <c r="A21" s="33"/>
+      <c r="B21" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.5">
-      <c r="A21" s="31"/>
-      <c r="B21" s="27" t="s">
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.5">
+      <c r="A22" s="33"/>
+      <c r="B22" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5">
-      <c r="A22" s="31"/>
-      <c r="B22" s="27" t="s">
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="16.5">
+      <c r="A23" s="33"/>
+      <c r="B23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5">
-      <c r="A23" s="31"/>
-      <c r="B23" s="27" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.5">
+      <c r="A24" s="33"/>
+      <c r="B24" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5">
-      <c r="A24" s="31"/>
-      <c r="B24" s="27" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="16.5">
+      <c r="A25" s="33"/>
+      <c r="B25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5">
-      <c r="A25" s="31"/>
-      <c r="B25" s="27" t="s">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" ht="16.5">
+      <c r="A26" s="33"/>
+      <c r="B26" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.5">
-      <c r="A26" s="31"/>
-      <c r="B26" s="27" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="16.5">
+      <c r="A27" s="33"/>
+      <c r="B27" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="31"/>
-      <c r="B27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="31"/>
-      <c r="B28" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="16.5">
@@ -1096,22 +1138,22 @@
     </row>
     <row r="30" spans="1:6" ht="28.5">
       <c r="A30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="C30" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
@@ -1149,39 +1191,56 @@
     <row r="35" spans="1:6" ht="16.5">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+    </row>
+    <row r="36" spans="1:6" ht="16.5">
+      <c r="A36" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-    </row>
-    <row r="36" spans="1:6" ht="16.5">
-      <c r="A36" s="36" t="s">
+      <c r="B36" s="24"/>
+      <c r="C36" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="38" t="s">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+    </row>
+    <row r="37" spans="1:6" ht="16.5">
+      <c r="A37" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-    </row>
-    <row r="37" spans="1:6" ht="16.5">
-      <c r="A37" s="37" t="s">
+      <c r="B37" s="25"/>
+      <c r="C37" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="A17:A28"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
@@ -1196,20 +1255,6 @@
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="A17:A28"/>
-    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
